--- a/Result/checksun_type/旅遊服務業.xlsx
+++ b/Result/checksun_type/旅遊服務業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>51.4</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>52.11</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>52.61</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>52.11</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>52.61</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>6535323.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>7347714.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>7347714.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>10333321.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>11978240.68</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>11978240.68</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1948295.088766223</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>6535323</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>6535323.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>51.26000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>52.64</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2740690.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>8011940.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>8011940.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>10806141.6</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>12386122.52</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>12386122.52</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-1915159.414465947</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2740690</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2740690.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>51.3</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>52.12</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>52.12</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>52.7</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3829549.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>10519715.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>10519715</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>12316595.9</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>12700637.78</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>12700637.78</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1392856.364948912</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3829549</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3829549.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>51.56</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>52.14</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>52.77</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>52.77</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>16500344.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>12054725.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>12054725.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>14524175.5</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>12830990.1</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>12830990.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-713627.7454621159</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>16500344</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>16500344.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>51.82000000000001</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>52.22</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>52.87</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>52.22</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>52.87</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>7132667.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>12549751.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>12549751.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>14490255.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>12743686.44</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>12743686.44</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1075399.619571619</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>7132667</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>7132667.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>52.0</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>52.94</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>52.94</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>9856452.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>13318927.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>13318927.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>19858784.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>12749559.38</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>12749559.38</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-550129.7747433484</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>9856452</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>9856452.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>52.46</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>52.38</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>53.02</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>53.02</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>15279563.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>13600342.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>13600342.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>21286928.8</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>12685447.98</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>12685447.98</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-71930.8973192703</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>15279563</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>15279563.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>52.73999999999999</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>52.44</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>53.08</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>53.08</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>11504600.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>14113476.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>14113476.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>20438055.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>12537891.86</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>12537891.86</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>32731.70961938798</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>11504600</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>11504600.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>52.96</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>52.49</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>53.11</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>53.11</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>18975476.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>16993625.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>16993625.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>20220510.5</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>12599032.82</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>12599032.82</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>585541.0513310656</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>18975476</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>18975476.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>53.27999999999999</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>53.19</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>53.19</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>10978547.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>16430760.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>16430760.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>19309948.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>12332361.88</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>12332361.88</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>553905.5019430667</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>10978547</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>10978547.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>53.34</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>52.49</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>53.25</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>53.25</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>11263528.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>26398642.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>26398642</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>19082139.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>12273526.76</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>12273526.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>1345743.342033673</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>11263528</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>11263528.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>11.78</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>9.57</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>6.97</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>6.97</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>482.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>405.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>405.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>344.6</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-47.12535053985937</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>482</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>482.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>11.79</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>9.28</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>6.85</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>6.85</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>267.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>352.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>352.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>305.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>0</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-63.67187944236076</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>267</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>267.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>11.84</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>8.98</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>6.73</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>6.73</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>410.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>320.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>320.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>298.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>0</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-62.00006789442125</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>410</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>410.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>11.91</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>8.64</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>6.61</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>6.61</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>139.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>302.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>302.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>286.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>0</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-72.71890611542125</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>139</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>11.9</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>8.26</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>6.47</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>6.47</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>730.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>394.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>394.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>319.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>0</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-56.39871406987055</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>730</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>730.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>11.89</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>7.89</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>6.33</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>6.33</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>215.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>283.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>283.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>276.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>0</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-94.39134278801697</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>215</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>215.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>12.31</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>6.21</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>107.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>259.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>259.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>347.4</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>0</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-90.11683585722551</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>107</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>11.282</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>7.24</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>6.09</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>6.09</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>320.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>276.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>276.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>553.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>0</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-69.22051038976548</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>320</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>10.182</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>6.89</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>5.96</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>5.96</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>599.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>270.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>270.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>995.2</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>0</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-59.7178843509023</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>599</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>599.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>9.032</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>6.52</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>5.83</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>5.83</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>177.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>244.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>244.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1101.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>0</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-73.90277985427974</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>177</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>177.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,21 +10087,17 @@
           <t>7.922</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>6.16</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
+      <c r="AM23" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AO23" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>5.7</t>
-        </is>
-      </c>
       <c r="AP23" t="inlineStr">
         <is>
           <t>124.99</t>
@@ -10268,20 +10138,16 @@
           <t>93.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>270.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>270.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1133.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>0</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-46.31324557859466</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>93</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>112.2</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>112.8</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>112.82</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>112.82</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>21037.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>26071.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>26071</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>48162.5</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>42213.76</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>42213.76</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-7548.486062300646</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>21037</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>21037.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>112.4</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>112.7</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>112.82</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>112.82</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>19058.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>30749.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>30749</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>49719.1</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>43407.58</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>43407.58</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-6469.215034162298</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>19058</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>19058.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>112.9</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>112.6</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>113</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>24807.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>48578.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>48578.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>59643.0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>45465.08</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>45465.08</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-4484.320171315994</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>24807</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>24807.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>113.9</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>112.55</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>113.16</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>113.16</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>35903.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>64943.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>64943.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>71050.0</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>47133.64</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>47133.64</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-2104.56607541714</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>35903</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>35903.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>114.9</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>112.65</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>113.45</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>113.45</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>29550.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>68359.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>68359.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>70924.4</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>49402.88</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>49402.88</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>181.3885642747045</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>29550</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>29550.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>115.3</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>112.68</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>113.59</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>112.68</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>113.59</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>44427.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>70254.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>70254</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>91726.7</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>51748.84</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>51748.84</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>4121.238457967527</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>44427</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>44427.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>115.5</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>112.72</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>113.64</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>112.72</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>113.64</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>108207.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>68689.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>68689.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>101378.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>51758.9</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>51758.9</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>8008.444075458436</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>108207</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>108207.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>115.1</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>112.7</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>113.63</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>113.63</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>106630.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>70707.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>70707.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>92274.5</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>50315.2</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>50315.2</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>6442.00766917906</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>106630</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>106630.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>114.9</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>112.55</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>113.52</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>113.52</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>52982.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>77156.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>77156.60000000001</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>83490.8</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>48729.14</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>48729.14</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>4143.133957737853</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>52982</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>52982.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>114.1</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>112.48</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>113.48</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>112.48</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>113.48</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>39024.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>73489.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>73489.60000000001</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>79330.1</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>48333.64</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>48333.64</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>6459.059585759765</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>39024</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>39024.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>113.2</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>112.38</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>113.43</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>112.38</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>113.43</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>36603.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>113199.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>113199.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>77059.1</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>48065.6</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>48065.6</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>11032.34406915681</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>36603</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>36603.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>83.12</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>87.24</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>90.92</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>90.92</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>8422.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>14225.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>14225.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>27181.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>47041.38</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>47041.38</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-9172.183915253685</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>8422</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>8422.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>83.12</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>87.49</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>91.4</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>87.48999999999999</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>91.40000000000001</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>11135.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>19609.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>19609.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>29051.0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>47958.04</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>47958.04</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-8664.966285010363</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>11135</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>11135.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>83.75999999999999</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>87.76</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>91.98</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>87.76000000000001</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>91.98</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>9638.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>28567.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>28567.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>32603.2</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>48393.18</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>48393.18</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-7921.585160198112</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>9638</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>9638.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>84.97999999999999</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>88.02</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>92.56</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>88.02</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>92.56</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>28598.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>34263.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>34263</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>41470.1</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>49205.26</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>49205.26</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-6416.305511887818</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>28598</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>28598.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>86.24000000000001</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>88.47</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>93.23</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>88.47</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>93.23</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>13333.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>34574.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>34574.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>42861.8</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>49894.06</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>49894.06</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-6068.180817448541</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>13333</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>13333.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>87.2</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>88.96</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>93.79</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>88.95999999999999</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>93.79000000000001</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>35342.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>40137.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>40137.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>66182.6</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>50217.24</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>50217.24</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-3718.603367626412</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>35342</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>35342.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>88.55999999999999</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>89.5</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>94.32</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>94.31999999999999</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>55928.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>38492.8</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>38492.8</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>84348.9</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>50166.46</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>50166.46</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-2587.364033322432</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>55928</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>55928.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>89.28</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>89.92</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>94.78</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>89.92</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>94.78</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>38114.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>36638.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>36638.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>80361.9</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>49614.36</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>49614.36</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-3084.544840269518</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>38114</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>38114.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>89.61999999999999</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>90.24</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>95.13</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>90.23999999999999</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>95.13</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>30154.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>48677.2</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>48677.2</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>78535.4</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>49189.82</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>49189.82</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-1775.997963041445</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>30154</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>30154.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>89.92</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>90.34</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>95.54</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>95.54000000000001</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>41150.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>51149.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>51149.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>78343.4</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>49178.8</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>49178.8</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>1009.640360250145</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>41150</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>41150.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>90.3</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>90.43</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>95.94</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>90.43000000000001</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>95.94</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>27118.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>92227.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>92227.60000000001</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>76705.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>48785.82</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>48785.82</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>3774.922237800623</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>27118</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>27118.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>18.82</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>19.86</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>19.86</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>3604.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>3574.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>3574.6</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>3281.7</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>4018.34</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>4018.34</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-476.8776452632655</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>3604</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>3604.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>18.78</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>19.87</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>19.87</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>2139.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>3144.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>3144.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>3468.3</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>4020.3</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>4020.3</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-544.6207990080648</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>2139</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>2139.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>18.8</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>19.72</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>19.9</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>2315.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>4046.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>4046.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>3613.9</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>4020.46</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>4020.46</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-464.9817043932044</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>2315</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>2315.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>19.02</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>19.77</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>19.92</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>19.92</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>2112.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>3940.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>3940.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>4096.1</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>4064.02</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>4064.02</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-353.4622226436459</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>2112</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>2112.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>19.27</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>19.84</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>19.96</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>19.96</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>7703.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>3884.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>3884</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>4607.7</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>4074.08</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>4074.08</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-159.7750264784308</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>7703</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>7703.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>19.49</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>19.91</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>20</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>1453.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>2988.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>2988.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>5896.2</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>3985.72</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>3985.72</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-476.4084952967532</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1453</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1453.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>19.74</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>19.98</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>20.02</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>6649.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>3792.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>3792.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>7291.8</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>4026.98</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>4026.98</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-242.0845759194717</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>6649</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>6649.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>20.03</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>20.04</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>20.04</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>1786.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>3181.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>3181.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>6761.9</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>3921.64</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>3921.64</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-455.4045276690886</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>1786</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>1786.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>20.13</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>20.09</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>20.04</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>20.04</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>1829.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>4251.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>4251.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>6806.1</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>3922.44</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>3922.44</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-222.8471541803592</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>1829</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>1829.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>20.3</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>20.04</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>20.04</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>3227.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>5331.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>5331.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>6894.4</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>3929.28</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>3929.28</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>112.7293491671244</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>3227</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>3227.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>20.48</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>20.04</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>20.04</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>5470.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>8803.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>8803.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>7005.2</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>3893.34</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>3893.34</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>438.3125914789889</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>5470</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>5470.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>179.7</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>171.12</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>163.88</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>171.12</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>163.88</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>130280265.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>159426303.2</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>159426303.2</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>265771809.4</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>157024764.8</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>157024764.8</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-21063863.35345381</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>130280265</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>130280265.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>179.8</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>170.02</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>163.48</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>170.02</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>163.48</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>103206813.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>181295516.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>181295516.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>269944859.9</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>160747101.4</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>160747101.4</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-14978099.84430227</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>103206813</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>103206813.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>179.4</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>168.98</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>163.22</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>168.98</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>163.22</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>164385720.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>253989911.8</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>253989911.8</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>300957920.5</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>163471827.72</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>163471827.72</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-2848492.83678925</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>164385720</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>164385720.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>179.8</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>167.88</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>162.85</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>167.88</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>162.85</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>144066171.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>349822253.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>349822253.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>344707301.2</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>171377084.82</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>171377084.82</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>8026366.168114662</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>144066171</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>144066171.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>178.5</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>166.88</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>162.71</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>166.88</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>162.71</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>255192547.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>380428524.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>380428524.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>359902982.6</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>176775093.54</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>176775093.54</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>25452317.63340187</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>255192547</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>255192547.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>176.8</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>165.95</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>162.43</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>165.95</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>162.43</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>239626331.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>372117315.6</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>372117315.6</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>411731326.4</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>179351445.66</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>179351445.66</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>37531125.23976219</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>239626331</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>239626331.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>175.1</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>165.05</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>162.25</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>165.05</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>162.25</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>466678790.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>358594203.4</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>358594203.4</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>406931495.1</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>182174395.24</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>182174395.24</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>55113976.20457107</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>466678790</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>466678790.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>173.7</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>164.35</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>162.06</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>164.35</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>162.06</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>643547429.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>347925929.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>347925929.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>365467175.5</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>178719989.06</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>178719989.06</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>53936929.25413471</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>643547429</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>643547429.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>172.1</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>163.38</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>161.67</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>163.38</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>161.67</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>297097525.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>339592348.8</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>339592348.8</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>309227604.7</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>169408707.3</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>169408707.3</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>31378903.38729224</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>297097525</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>297097525.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>171.3</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>162.75</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>161.45</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>162.75</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>161.45</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>213636503.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>339377440.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>339377440.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>298972151.3</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>169236797.24</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>169236797.24</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>35152109.59939981</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>213636503</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>213636503.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>170.4</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>162.07</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>161.19</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>162.07</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>161.19</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>172010770.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>451345337.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>451345337.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>283282576.2</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>168969476.52</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>168969476.52</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>48229224.0595749</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>172010770</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>172010770.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>31.34</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>34.21</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>34.35</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>34.35</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>162.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>503.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>503</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>879.6</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>1918.06</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>1918.06</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-618.1466327049411</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>162</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>31.4</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>34.45</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>283.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>529.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>529.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>990.7</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>1939.24</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>1939.24</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-607.1782883159431</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>283</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>283.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>31.54</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>34.41</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>34.56</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>34.56</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>563.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>979.2</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>979.2</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>1180.8</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>1948.06</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>1948.06</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-582.7885717489478</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>563</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>563.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>32.02</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>34.54</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>34.68</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>34.68</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>1002.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>1116.2</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>1116.2</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>1395.8</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>1957.9</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>1957.9</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-557.1322419479209</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>1002</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>1002.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>32.85</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>34.69</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>34.69</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>34.8</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>505.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>1064.6</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>1064.6</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>1665.7</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>1948.14</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>1948.14</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-547.6184764483141</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>505</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>505.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>33.48999999999999</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>34.92</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>34.92</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>294.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>1256.2</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>1256.2</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>4839.3</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>1947.12</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>1947.12</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-461.2195801471503</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>294</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>294.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>34.29</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>34.91</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>35.03</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>34.91</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>35.03</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>2532.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>1452.0</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>1452</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>5914.6</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>1949.46</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>1949.46</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-298.7133147116606</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>2532</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>2532.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>35.02</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>35.02</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>35.13</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>35.13</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>1248.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>1382.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>1382.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>5706.6</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>1921.72</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>1921.72</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-295.6788885641158</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>1248</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>1248.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>35.8</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>35.08</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>35.2</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>35.08</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>35.2</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>744.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>1675.4</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>1675.4</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>5642.1</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>1896.8</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>1896.8</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-143.2126051903333</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>744</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>744.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>36.47000000000001</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>34.9</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>35.25</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>35.25</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>1463.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>2266.8</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>2266.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>5692.9</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>1899.5</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>1899.5</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>133.7111069575822</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>1463</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>1463.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>37.08</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>34.76</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>35.31</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>34.76</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>35.31</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>1273.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>8422.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>8422.4</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>5587.2</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>1875.04</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>1875.04</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>447.5052990632612</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>1273</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>1273.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
